--- a/tabelas/FT_PRODPERIG.xlsx
+++ b/tabelas/FT_PRODPERIG.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/99477d7318b1e097/14. Gisele^0Jardel/Atuá Estratégia ^0 Análises/8. Projetos/STANG/5.MotorCalculo/MotorTransporte/tabelas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/99477d7318b1e097/14. Gisele^0Jardel/Atuá Estratégia ^0 Análises/8. Projetos/STANG/5.MotorCalculo/01_RC_Ambiental/MotorTransporteV5/tabelas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="8_{DFC3E348-208D-46DA-AF79-9C05C50133E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FF0BA70-AAE5-44EF-872D-43AC61A788D1}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="8_{DFC3E348-208D-46DA-AF79-9C05C50133E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1173C41F-9AC5-4591-A032-28DE2DCA6C37}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{77FAD20C-44E5-4827-8893-D4E5A201625A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{77FAD20C-44E5-4827-8893-D4E5A201625A}"/>
   </bookViews>
   <sheets>
     <sheet name="FT_PRODPERIG" sheetId="1" r:id="rId1"/>
@@ -606,7 +606,7 @@
         <v>15</v>
       </c>
       <c r="D2" s="8">
-        <v>1.024716</v>
+        <v>1</v>
       </c>
       <c r="E2" s="8">
         <v>1</v>
@@ -642,7 +642,7 @@
         <v>1.01</v>
       </c>
       <c r="P2" s="9">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="Q2" s="9">
         <v>1</v>
@@ -695,7 +695,7 @@
         <v>1</v>
       </c>
       <c r="P3" s="9">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="Q3" s="9">
         <v>1</v>
